--- a/Employee_Reports_wi52/Alvin Tumboc Cuevas Q0545.xlsx
+++ b/Employee_Reports_wi52/Alvin Tumboc Cuevas Q0545.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>672</v>
+        <v>664</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1363,11 +1363,11 @@
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1412,11 +1412,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1449,11 +1449,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1498,11 +1498,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1547,11 +1547,11 @@
         </is>
       </c>
       <c r="H23" s="5" t="n">
-        <v>-24</v>
+        <v>-32</v>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
@@ -1584,11 +1584,11 @@
         </is>
       </c>
       <c r="H24" s="5" t="n">
-        <v>-24</v>
+        <v>-32</v>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
@@ -1599,41 +1599,41 @@
       <c r="K24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>POWERED ROLLER DECK(matarSOP) (SOPs)</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr"/>
-      <c r="D25" s="3" t="inlineStr"/>
-      <c r="E25" s="3" t="inlineStr"/>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr"/>
+      <c r="D25" s="4" t="inlineStr"/>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>01-Oct-2025</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>01-Oct-2026</t>
         </is>
       </c>
-      <c r="H25" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr"/>
+      <c r="H25" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -1670,11 +1670,11 @@
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -1719,11 +1719,11 @@
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -1756,11 +1756,11 @@
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -1805,11 +1805,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -1842,11 +1842,11 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7911</v>
+        <v>7903</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7947</v>
+        <v>7939</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7947</v>
+        <v>7939</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7947</v>
+        <v>7939</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7947</v>
+        <v>7939</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7947</v>
+        <v>7939</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7951</v>
+        <v>7943</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7954</v>
+        <v>7946</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7954</v>
+        <v>7946</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7954</v>
+        <v>7946</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7954</v>
+        <v>7946</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7954</v>
+        <v>7946</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7951</v>
+        <v>7943</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7951</v>
+        <v>7943</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7951</v>
+        <v>7943</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7955</v>
+        <v>7947</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7955</v>
+        <v>7947</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7951</v>
+        <v>7943</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7955</v>
+        <v>7947</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
